--- a/output/pdf_financials_xlsx/ENCR.xlsx
+++ b/output/pdf_financials_xlsx/ENCR.xlsx
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.000927</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.155393</v>
       </c>
     </row>
     <row r="93">
@@ -2564,7 +2564,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>0.000927</v>
       </c>

--- a/output/pdf_financials_xlsx/ENCR.xlsx
+++ b/output/pdf_financials_xlsx/ENCR.xlsx
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.022635</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.805521</v>
       </c>
     </row>
     <row r="35">
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.022635</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.805521</v>
       </c>
     </row>
     <row r="37">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">

--- a/output/pdf_financials_xlsx/ENCR.xlsx
+++ b/output/pdf_financials_xlsx/ENCR.xlsx
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.027063</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.019688</v>
       </c>
     </row>
     <row r="68">
